--- a/ig/DM_FINESS_New/ValueSet-jdv-j331-type-act-sociale-regulee-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j331-type-act-sociale-regulee-finess.xlsx
@@ -102,7 +102,7 @@
     <t>=</t>
   </si>
   <si>
-    <t>ASOCR</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r374-nature-activite-smsse-regulee|ASOCR</t>
   </si>
   <si>
     <t/>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j331-type-act-sociale-regulee-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j331-type-act-sociale-regulee-finess.xlsx
@@ -102,7 +102,7 @@
     <t>=</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r374-nature-activite-smsse-regulee|ASOCR</t>
+    <t>ASOCR</t>
   </si>
   <si>
     <t/>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j331-type-act-sociale-regulee-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j331-type-act-sociale-regulee-finess.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j322-type-act-enseignement-regulee-finess</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j331-type-act-sociale-regulee-finess</t>
   </si>
   <si>
     <t>Identifier</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j331-type-act-sociale-regulee-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j331-type-act-sociale-regulee-finess.xlsx
@@ -102,7 +102,7 @@
     <t>=</t>
   </si>
   <si>
-    <t>ASOCR</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r374-nature-activite-smsse-regulee#ASOCR</t>
   </si>
   <si>
     <t/>
